--- a/Output/万物有灵独特效果汇总.xlsx
+++ b/Output/万物有灵独特效果汇总.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>万物有灵独特效果汇总</t>
+          <t>万物有灵独特效果汇总（源码 4.9）</t>
         </is>
       </c>
     </row>

--- a/Output/万物有灵独特效果汇总.xlsx
+++ b/Output/万物有灵独特效果汇总.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>万物有灵独特效果汇总（源码 4.9）</t>
+          <t>万物有灵独特效果汇总（源码 4.13）</t>
         </is>
       </c>
     </row>
